--- a/domestic_customer_IND_sample.xlsx
+++ b/domestic_customer_IND_sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBA1630-B4B5-4E1C-BB18-374942799C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B76EB932-3AAF-4225-80E7-D1FB9719689A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="179">
+  <si>
+    <t>Transaction Code</t>
+  </si>
   <si>
     <t>New Customer Code</t>
   </si>
@@ -40,6 +43,24 @@
     <t>Customer Account Group</t>
   </si>
   <si>
+    <t>Reference for customer (matchcode field)</t>
+  </si>
+  <si>
+    <t>Reference Company Code</t>
+  </si>
+  <si>
+    <t>Reference sales organization</t>
+  </si>
+  <si>
+    <t>Reference distribution channel</t>
+  </si>
+  <si>
+    <t>Division that is used as a reference</t>
+  </si>
+  <si>
+    <t>ALWAYS X</t>
+  </si>
+  <si>
     <t>Title text</t>
   </si>
   <si>
@@ -401,6 +422,9 @@
   </si>
   <si>
     <t>Location Number</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>1000</t>
@@ -902,584 +926,608 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:EF2"/>
+  <dimension ref="A1:EF2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:136" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:136" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="T1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="U1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="W1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="X1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Y1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Z1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AA1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AB1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AC1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AD1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AE1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AF1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AG1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AH1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="AI1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AJ1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="AK1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AL1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="AM1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="AN1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="AO1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="AP1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="AQ1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AR1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="AS1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AT1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AU1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AV1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="AW1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="AX1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="AY1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="AZ1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="BA1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="BB1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="BC1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="BD1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BE1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="BF1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="BG1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="BH1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="BI1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" t="s">
         <v>53</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>55</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>56</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>59</v>
-      </c>
-      <c r="BP1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BQ1" t="s">
+      <c r="BX1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>76</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>79</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>80</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>81</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>82</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>83</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>84</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>90</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>93</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>94</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>96</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>97</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>98</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>101</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>102</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>103</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>104</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>105</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>106</v>
+      </c>
+      <c r="DE1" t="s">
+        <v>107</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>108</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>109</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>110</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>111</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>112</v>
+      </c>
+      <c r="DK1" t="s">
+        <v>113</v>
+      </c>
+      <c r="DL1" t="s">
+        <v>114</v>
+      </c>
+      <c r="DM1" t="s">
         <v>61</v>
       </c>
-      <c r="BR1" t="s">
-        <v>62</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>64</v>
-      </c>
-      <c r="BU1" t="s">
-        <v>65</v>
-      </c>
-      <c r="BV1" t="s">
-        <v>66</v>
-      </c>
-      <c r="BW1" t="s">
-        <v>46</v>
-      </c>
-      <c r="BX1" t="s">
-        <v>67</v>
-      </c>
-      <c r="BY1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BZ1" t="s">
-        <v>69</v>
-      </c>
-      <c r="CA1" t="s">
-        <v>70</v>
-      </c>
-      <c r="CB1" t="s">
-        <v>71</v>
-      </c>
-      <c r="CC1" t="s">
-        <v>72</v>
-      </c>
-      <c r="CD1" t="s">
-        <v>73</v>
-      </c>
-      <c r="CE1" t="s">
-        <v>74</v>
-      </c>
-      <c r="CF1" t="s">
-        <v>75</v>
-      </c>
-      <c r="CG1" t="s">
-        <v>76</v>
-      </c>
-      <c r="CH1" t="s">
-        <v>77</v>
-      </c>
-      <c r="CI1" t="s">
-        <v>78</v>
-      </c>
-      <c r="CJ1" t="s">
-        <v>79</v>
-      </c>
-      <c r="CK1" t="s">
-        <v>80</v>
-      </c>
-      <c r="CL1" t="s">
-        <v>81</v>
-      </c>
-      <c r="CM1" t="s">
-        <v>82</v>
-      </c>
-      <c r="CN1" t="s">
-        <v>83</v>
-      </c>
-      <c r="CO1" t="s">
-        <v>84</v>
-      </c>
-      <c r="CP1" t="s">
-        <v>85</v>
-      </c>
-      <c r="CQ1" t="s">
-        <v>86</v>
-      </c>
-      <c r="CR1" t="s">
-        <v>87</v>
-      </c>
-      <c r="CS1" t="s">
-        <v>88</v>
-      </c>
-      <c r="CT1" t="s">
-        <v>89</v>
-      </c>
-      <c r="CU1" t="s">
-        <v>90</v>
-      </c>
-      <c r="CV1" t="s">
-        <v>91</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CX1" t="s">
-        <v>93</v>
-      </c>
-      <c r="CY1" t="s">
-        <v>94</v>
-      </c>
-      <c r="CZ1" t="s">
-        <v>95</v>
-      </c>
-      <c r="DA1" t="s">
-        <v>96</v>
-      </c>
-      <c r="DB1" t="s">
-        <v>97</v>
-      </c>
-      <c r="DC1" t="s">
-        <v>98</v>
-      </c>
-      <c r="DD1" t="s">
-        <v>99</v>
-      </c>
-      <c r="DE1" t="s">
-        <v>100</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>101</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>102</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>103</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>104</v>
-      </c>
-      <c r="DJ1" t="s">
-        <v>105</v>
-      </c>
-      <c r="DK1" t="s">
-        <v>106</v>
-      </c>
-      <c r="DL1" t="s">
-        <v>107</v>
-      </c>
-      <c r="DM1" t="s">
-        <v>54</v>
-      </c>
       <c r="DN1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="DO1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="DP1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="DQ1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="DR1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="DS1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="DT1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="DU1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="DV1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="DW1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="DX1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="DY1" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="DZ1" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="EA1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="EB1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="EC1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="ED1" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="EE1" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="EF1" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
-    <row r="2" spans="2:136" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:136" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>134</v>
+      </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="O2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="S2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="V2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="X2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="Z2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="AB2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="AC2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="AD2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="AE2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AF2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="AG2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="AH2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="AK2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="AM2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="AR2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>157</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>159</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>160</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>161</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>162</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>164</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>165</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>166</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>167</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>157</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>159</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>157</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>168</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>157</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>167</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>167</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>167</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>167</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>167</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>167</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>170</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>157</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>157</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>168</v>
+      </c>
+      <c r="CK2" t="s">
+        <v>171</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>172</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>174</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>175</v>
+      </c>
+      <c r="DL2" t="s">
+        <v>176</v>
+      </c>
+      <c r="DM2" t="s">
+        <v>164</v>
+      </c>
+      <c r="DP2" t="s">
         <v>144</v>
       </c>
-      <c r="AV2" t="s">
-        <v>145</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>146</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>147</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>149</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>151</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>153</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>154</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>155</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>156</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>157</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>158</v>
-      </c>
-      <c r="BO2" t="s">
-        <v>159</v>
-      </c>
-      <c r="BP2" t="s">
-        <v>149</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>151</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>149</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>160</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>161</v>
-      </c>
-      <c r="BW2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BX2" t="s">
-        <v>149</v>
-      </c>
-      <c r="BY2" t="s">
-        <v>159</v>
-      </c>
-      <c r="BZ2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CA2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CB2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CC2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CE2" t="s">
-        <v>162</v>
-      </c>
-      <c r="CG2" t="s">
-        <v>149</v>
-      </c>
-      <c r="CH2" t="s">
-        <v>149</v>
-      </c>
-      <c r="CJ2" t="s">
-        <v>160</v>
-      </c>
-      <c r="CK2" t="s">
-        <v>163</v>
-      </c>
-      <c r="CL2" t="s">
-        <v>164</v>
-      </c>
-      <c r="CM2" t="s">
-        <v>165</v>
-      </c>
-      <c r="CO2" t="s">
-        <v>166</v>
-      </c>
-      <c r="CQ2" t="s">
-        <v>167</v>
-      </c>
-      <c r="DL2" t="s">
-        <v>168</v>
-      </c>
-      <c r="DM2" t="s">
-        <v>156</v>
-      </c>
-      <c r="DP2" t="s">
-        <v>136</v>
-      </c>
       <c r="DQ2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="DS2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
